--- a/src/main/resources/uploadfiles/DCM_VIDEO_BulkUpload.xlsx
+++ b/src/main/resources/uploadfiles/DCM_VIDEO_BulkUpload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsherkar\IdeaProjects\PulsePointNew\src\main\resources\uploadfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB93F15-EC35-4065-8D35-39A2D0DE376D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9F5C54-409E-4905-9E9D-6FECA3A50E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{F7256278-5325-46C9-B06E-40D6ED4DCF2C}"/>
   </bookViews>
@@ -411,26 +411,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -894,23 +894,23 @@
   <sheetData>
     <row r="1" spans="2:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
@@ -1009,38 +1009,38 @@
     </row>
     <row r="8" spans="2:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" spans="2:23" ht="112.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
     </row>
     <row r="11" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4"/>
@@ -1061,26 +1061,26 @@
       </c>
     </row>
     <row r="13" spans="2:23" ht="15.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="20" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
@@ -1303,6 +1303,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="15">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B10:N10"/>
     <mergeCell ref="O13:Q13"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="I4:N4"/>
@@ -1313,11 +1318,6 @@
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="I7:N7"/>
     <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="B9:N9"/>
-    <mergeCell ref="B10:N10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1" display="https://ad.doubleclick.net/ddm/pfadx/N1889303.3848558MATTERKIND7/B32723320.408487114;sz=800x250;dsp_id_0_=64;dsp_xappb_0_=INSERTMACROHERE;ord=[timestamp];dc_lat=;dc_rdid=;tag_for_child_directed_treatment=;tfua=;dc_tdv=1;dcmt=text/xml;dc_sdk_apis=[APIFRAMEWORKS];dc_omid_p=[OMIDPARTNER];gdpr=${GDPR};gdpr_consent=${GDPR_CONSENT_755};dc_mpos=[BREAKPOSITION];ltd=" xr:uid="{8DDB3F24-97B9-49CD-9A8C-09843EEE5242}"/>
@@ -1329,12 +1329,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="67a22a66-1624-4d4d-8bc2-edbd80716107"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="73ad4f0a-cdb3-41e8-a324-87698dc7e764">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1587,20 +1589,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="67a22a66-1624-4d4d-8bc2-edbd80716107"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="73ad4f0a-cdb3-41e8-a324-87698dc7e764">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB24A93E-D7FB-4D92-B735-0CC7822803C2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A10B3CC4-2747-4758-BFA4-588CF47A434C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="67a22a66-1624-4d4d-8bc2-edbd80716107"/>
+    <ds:schemaRef ds:uri="73ad4f0a-cdb3-41e8-a324-87698dc7e764"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1625,12 +1628,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A10B3CC4-2747-4758-BFA4-588CF47A434C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB24A93E-D7FB-4D92-B735-0CC7822803C2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="67a22a66-1624-4d4d-8bc2-edbd80716107"/>
-    <ds:schemaRef ds:uri="73ad4f0a-cdb3-41e8-a324-87698dc7e764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>